--- a/T01/downloads/DG-T01 Turnkey BOQ.xlsx
+++ b/T01/downloads/DG-T01 Turnkey BOQ.xlsx
@@ -2358,7 +2358,7 @@
         </is>
       </c>
       <c r="C56" s="8" t="n">
-        <v>291</v>
+        <v>266</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -3270,7 +3270,7 @@
         </is>
       </c>
       <c r="C90" s="8" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>

--- a/T01/downloads/DG-T01 Turnkey BOQ.xlsx
+++ b/T01/downloads/DG-T01 Turnkey BOQ.xlsx
@@ -3815,7 +3815,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Downpipe sets 68 round black</t>
+          <t>Downpipe sets 68 round black: swan neck to the outlet, clipped to the side wall (4 clips), shoe</t>
         </is>
       </c>
       <c r="C12" s="8" t="n">
